--- a/artfynd/A 9741-2026 artfynd.xlsx
+++ b/artfynd/A 9741-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1976133</v>
+        <v>1894805</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580023.5144773189</v>
+        <v>580024</v>
       </c>
       <c r="R2" t="n">
-        <v>7047372.196566993</v>
+        <v>7047372</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2011-08-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,12 +790,7 @@
         <v>1906184</v>
       </c>
       <c r="B3" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580023.5144773189</v>
+        <v>580024</v>
       </c>
       <c r="R3" t="n">
-        <v>7047372.196566993</v>
+        <v>7047372</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +855,9 @@
           <t>2011-08-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-08-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,37 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1894805</v>
+        <v>1976133</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580023.5144773189</v>
+        <v>580024</v>
       </c>
       <c r="R4" t="n">
-        <v>7047372.196566993</v>
+        <v>7047372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,19 +967,9 @@
           <t>2011-08-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-08-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,12 +1014,7 @@
         <v>1920750</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580023.5144773189</v>
+        <v>580024</v>
       </c>
       <c r="R5" t="n">
-        <v>7047372.196566993</v>
+        <v>7047372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,19 +1079,9 @@
           <t>2011-08-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-08-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 9741-2026 artfynd.xlsx
+++ b/artfynd/A 9741-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1894805</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1906184</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1976133</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,8 +1140,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1920750</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>